--- a/docs/files/REPORT_FILTRI/CR - GRAZIOSI DAVIDE.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - GRAZIOSI DAVIDE.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N19" headerRowCount="1">
-  <autoFilter ref="A10:N19"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N20" headerRowCount="1">
+  <autoFilter ref="A10:N20"/>
   <tableColumns count="14">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -673,16 +673,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>842</v>
+        <v>1148</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>591</v>
+        <v>789</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>424</v>
+        <v>590</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>435</v>
+        <v>579</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>341</v>
+        <v>451</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>298</v>
+        <v>381</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>142</v>
+        <v>203</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>381</v>
+        <v>516</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>276</v>
+        <v>377</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>145</v>
+        <v>199</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>314</v>
+        <v>430</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>118</v>
+        <v>191</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>192</v>
+        <v>266</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>167</v>
+        <v>219</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,35 +929,35 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J14" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K14" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L14" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="M14" s="12" t="n">
         <v>6</v>
-      </c>
-      <c r="L14" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="M14" s="12" t="n">
-        <v>4</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,28 +1037,28 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I15" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="J15" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K15" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="J15" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K15" s="12" t="n">
-        <v>9</v>
-      </c>
       <c r="L15" s="12" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>3</v>
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>2</v>
@@ -1103,23 +1103,23 @@
         <v>1</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J16" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K16" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K16" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="L16" s="12" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1145,47 +1145,47 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I17" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="J17" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K17" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I17" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="J17" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K17" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="L17" s="12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>01671</t>
+          <t>11725</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>BRESCIA</t>
+          <t>GAVARDO</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1199,47 +1199,47 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J18" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>11725</t>
+          <t>01671</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>GAVARDO</t>
+          <t>BRESCIA</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1253,35 +1253,85 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>24</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J19" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>01658</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>BRESCIA</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>GRAZIOSI DAVIDE</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/CR - GRAZIOSI DAVIDE.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - GRAZIOSI DAVIDE.xlsx
@@ -535,7 +535,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -845,7 +845,7 @@
         <v>516</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.1182170542635659</v>
+        <v>61</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>219</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.0228310502283105</v>
+        <v>5</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>42</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0.07142857142857142</v>
+        <v>3</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>38</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0.1578947368421053</v>
+        <v>6</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>40</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>0.075</v>
+        <v>3</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>24</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.2083333333333333</v>
+        <v>5</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>25</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.08</v>
+        <v>2</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/CR - GRAZIOSI DAVIDE.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - GRAZIOSI DAVIDE.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>10</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1148</v>
+        <v>1204</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>789</v>
+        <v>818</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>590</v>
+        <v>625</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>579</v>
+        <v>622</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>451</v>
+        <v>479</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>381</v>
+        <v>400</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>516</v>
+        <v>542</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>430</v>
+        <v>452</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>5</v>
@@ -929,35 +929,35 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="F13" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="F13" s="12" t="n">
-        <v>47</v>
-      </c>
       <c r="G13" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>3</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -983,10 +983,10 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>8</v>
@@ -995,7 +995,7 @@
         <v>2</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J14" s="12" t="n">
         <v>4</v>
@@ -1004,10 +1004,10 @@
         <v>9</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>2</v>
@@ -1103,7 +1103,7 @@
         <v>1</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J16" s="12" t="n">
         <v>5</v>
@@ -1112,7 +1112,7 @@
         <v>4</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
@@ -1148,7 +1148,7 @@
         <v>21</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>2</v>
@@ -1166,10 +1166,10 @@
         <v>3</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1199,16 +1199,16 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>24</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>9</v>
@@ -1217,10 +1217,10 @@
         <v>1</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>2</v>
@@ -1259,10 +1259,10 @@
         <v>10</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>8</v>
@@ -1274,7 +1274,7 @@
         <v>0</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
@@ -1306,7 +1306,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/CR - GRAZIOSI DAVIDE.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - GRAZIOSI DAVIDE.xlsx
@@ -1028,7 +1028,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">

--- a/docs/files/REPORT_FILTRI/CR - GRAZIOSI DAVIDE.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - GRAZIOSI DAVIDE.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>10</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1204</v>
+        <v>1299</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>818</v>
+        <v>878</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>625</v>
+        <v>676</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>622</v>
+        <v>678</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>479</v>
+        <v>497</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>400</v>
+        <v>438</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>542</v>
+        <v>574</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,35 +875,35 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>384</v>
+        <v>408</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>452</v>
+        <v>487</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>5</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -929,19 +929,19 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="F13" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="F13" s="12" t="n">
-        <v>48</v>
-      </c>
       <c r="G13" s="12" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>66</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J13" s="12" t="n">
         <v>11</v>
@@ -950,14 +950,14 @@
         <v>15</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>3</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F14" s="12" t="n">
         <v>58</v>
@@ -1001,13 +1001,13 @@
         <v>4</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1018,12 +1018,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>11726</t>
+          <t>55973</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>REZZATO</t>
+          <t>BOTTICINO</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1037,47 +1037,47 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>55973</t>
+          <t>11726</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>BOTTICINO</t>
+          <t>REZZATO</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1091,35 +1091,35 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>2</v>
@@ -1157,7 +1157,7 @@
         <v>5</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J17" s="12" t="n">
         <v>6</v>
@@ -1166,10 +1166,10 @@
         <v>3</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1199,16 +1199,16 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>9</v>
@@ -1217,10 +1217,10 @@
         <v>1</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>2</v>
@@ -1256,13 +1256,13 @@
         <v>11</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>8</v>

--- a/docs/files/REPORT_FILTRI/CR - GRAZIOSI DAVIDE.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - GRAZIOSI DAVIDE.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>10</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1299</v>
+        <v>1370</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>878</v>
+        <v>931</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>676</v>
+        <v>716</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>678</v>
+        <v>715</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>497</v>
+        <v>517</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>54</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>438</v>
+        <v>465</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>574</v>
+        <v>597</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>408</v>
+        <v>433</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>487</v>
+        <v>517</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>5</v>
@@ -929,28 +929,28 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="F13" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="F13" s="12" t="n">
-        <v>49</v>
-      </c>
       <c r="G13" s="12" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J13" s="12" t="n">
         <v>11</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>3</v>
@@ -986,7 +986,7 @@
         <v>39</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>8</v>
@@ -1040,7 +1040,7 @@
         <v>37</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G15" s="12" t="n">
         <v>2</v>
@@ -1058,14 +1058,14 @@
         <v>8</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>16</v>
@@ -1109,10 +1109,10 @@
         <v>8</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>3</v>
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J17" s="12" t="n">
         <v>6</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>38</v>
@@ -1208,10 +1208,10 @@
         <v>25</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J18" s="12" t="n">
         <v>1</v>
@@ -1220,10 +1220,10 @@
         <v>10</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>30</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>8</v>
@@ -1306,13 +1306,13 @@
         <v>0</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I20" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/CR - GRAZIOSI DAVIDE.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - GRAZIOSI DAVIDE.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>10</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1370</v>
+        <v>1449</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>931</v>
+        <v>972</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>716</v>
+        <v>751</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>715</v>
+        <v>758</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>517</v>
+        <v>550</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>465</v>
+        <v>482</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>255</v>
+        <v>281</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>597</v>
+        <v>641</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,35 +875,35 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>433</v>
+        <v>453</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>517</v>
+        <v>543</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -932,13 +932,13 @@
         <v>52</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G13" s="12" t="n">
         <v>85</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>37</v>
@@ -950,14 +950,14 @@
         <v>16</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>3</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -983,19 +983,19 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J14" s="12" t="n">
         <v>4</v>
@@ -1004,7 +1004,7 @@
         <v>10</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>8</v>
@@ -1018,12 +1018,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>55973</t>
+          <t>11726</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>BOTTICINO</t>
+          <t>REZZATO</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1037,47 +1037,47 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>11726</t>
+          <t>55973</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>REZZATO</t>
+          <t>BOTTICINO</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1091,31 +1091,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="L16" s="12" t="n">
         <v>43</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1145,28 +1145,28 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>3</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>7</v>
@@ -1199,28 +1199,28 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J18" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>3</v>
@@ -1256,13 +1256,13 @@
         <v>11</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>30</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>8</v>
@@ -1306,7 +1306,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/CR - GRAZIOSI DAVIDE.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - GRAZIOSI DAVIDE.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Emanuele Marcelli</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Emanuele Marcelli</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Emanuele Marcelli</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Emanuele Marcelli</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">

--- a/docs/files/REPORT_FILTRI/CR - GRAZIOSI DAVIDE.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - GRAZIOSI DAVIDE.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Emanuele Marcelli</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Emanuele Marcelli</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Emanuele Marcelli</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Emanuele Marcelli</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">

--- a/docs/files/REPORT_FILTRI/CR - GRAZIOSI DAVIDE.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - GRAZIOSI DAVIDE.xlsx
@@ -209,23 +209,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N20" headerRowCount="1">
-  <autoFilter ref="A10:N20"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O20" headerRowCount="1">
+  <autoFilter ref="A10:O20"/>
+  <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
-    <tableColumn id="3" name="Agente"/>
-    <tableColumn id="4" name="CR"/>
-    <tableColumn id="5" name="Vend 2026"/>
-    <tableColumn id="6" name="Vend 2025"/>
-    <tableColumn id="7" name="Ass 2026"/>
-    <tableColumn id="8" name="Ass 2025"/>
-    <tableColumn id="9" name="Prospect"/>
-    <tableColumn id="10" name="Twin"/>
-    <tableColumn id="11" name="Business"/>
-    <tableColumn id="12" name="Sost anno"/>
-    <tableColumn id="13" name="UP EU"/>
-    <tableColumn id="14" name="Stato"/>
+    <tableColumn id="3" name="Indirizzo"/>
+    <tableColumn id="4" name="Agente"/>
+    <tableColumn id="5" name="CR"/>
+    <tableColumn id="6" name="Vend 2026"/>
+    <tableColumn id="7" name="Vend 2025"/>
+    <tableColumn id="8" name="Ass 2026"/>
+    <tableColumn id="9" name="Ass 2025"/>
+    <tableColumn id="10" name="Prospect"/>
+    <tableColumn id="11" name="Twin"/>
+    <tableColumn id="12" name="Business"/>
+    <tableColumn id="13" name="Sost anno"/>
+    <tableColumn id="14" name="UP EU"/>
+    <tableColumn id="15" name="Stato"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -520,23 +521,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -558,6 +560,7 @@
       <c r="L1" s="2" t="n"/>
       <c r="M1" s="2" t="n"/>
       <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -574,6 +577,7 @@
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -598,6 +602,7 @@
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -622,6 +627,7 @@
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -638,6 +644,7 @@
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -670,6 +677,7 @@
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -694,6 +702,7 @@
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -710,6 +719,7 @@
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -726,6 +736,7 @@
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -740,60 +751,65 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
+          <t>Indirizzo</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>CR</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Vend 2026</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Vend 2025</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>Ass 2026</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>Ass 2025</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>Twin</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Sost anno</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>UP EU</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
@@ -812,42 +828,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>VIA DALMAZIA 44</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Emanuele</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>758</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>550</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="H11" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="I11" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="I11" s="12" t="n">
+      <c r="J11" s="12" t="n">
         <v>482</v>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="K11" s="12" t="n">
         <v>159</v>
       </c>
-      <c r="K11" s="12" t="n">
+      <c r="L11" s="12" t="n">
         <v>281</v>
       </c>
-      <c r="L11" s="12" t="n">
+      <c r="M11" s="12" t="n">
         <v>641</v>
       </c>
-      <c r="M11" s="12" t="n">
+      <c r="N11" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -866,42 +887,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>S S 11 KM 224 + 521</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Emanuele</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>453</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>248</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="H12" s="12" t="n">
         <v>543</v>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="I12" s="12" t="n">
         <v>263</v>
       </c>
-      <c r="I12" s="12" t="n">
+      <c r="J12" s="12" t="n">
         <v>318</v>
       </c>
-      <c r="J12" s="12" t="n">
+      <c r="K12" s="12" t="n">
         <v>123</v>
       </c>
-      <c r="K12" s="12" t="n">
+      <c r="L12" s="12" t="n">
         <v>134</v>
       </c>
-      <c r="L12" s="12" t="n">
+      <c r="M12" s="12" t="n">
         <v>261</v>
       </c>
-      <c r="M12" s="12" t="n">
+      <c r="N12" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -920,42 +946,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>SS 45 BIS KM 55+370</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Emanuele</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>GRAZIOSI DAVIDE</t>
         </is>
-      </c>
-      <c r="E13" s="12" t="n">
-        <v>52</v>
       </c>
       <c r="F13" s="12" t="n">
         <v>52</v>
       </c>
       <c r="G13" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="H13" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="I13" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="I13" s="12" t="n">
+      <c r="J13" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="K13" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="K13" s="12" t="n">
+      <c r="L13" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="L13" s="12" t="n">
+      <c r="M13" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="M13" s="12" t="n">
+      <c r="N13" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -974,42 +1005,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>CA' BIANCA SS 39</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="H14" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="H14" s="12" t="n">
+      <c r="I14" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I14" s="12" t="n">
+      <c r="J14" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="J14" s="12" t="n">
+      <c r="K14" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K14" s="12" t="n">
+      <c r="L14" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="L14" s="12" t="n">
+      <c r="M14" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="M14" s="12" t="n">
+      <c r="N14" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1028,42 +1064,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>S.S.45 KM.49+300</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Emanuele</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="H15" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="I15" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I15" s="12" t="n">
+      <c r="J15" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="J15" s="12" t="n">
+      <c r="K15" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="K15" s="12" t="n">
+      <c r="L15" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="L15" s="12" t="n">
+      <c r="M15" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="M15" s="12" t="n">
+      <c r="N15" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1082,42 +1123,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>GARIBALDI 18</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Emanuele</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="H16" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H16" s="12" t="n">
+      <c r="I16" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="12" t="n">
+      <c r="J16" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="J16" s="12" t="n">
+      <c r="K16" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K16" s="12" t="n">
+      <c r="L16" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L16" s="12" t="n">
+      <c r="M16" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="M16" s="12" t="n">
+      <c r="N16" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1136,42 +1182,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>VIA NAZIONALE 1146</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
           <t>Fabio Villa</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="H17" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H17" s="12" t="n">
+      <c r="I17" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I17" s="12" t="n">
+      <c r="J17" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="K17" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="K17" s="12" t="n">
+      <c r="L17" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="L17" s="12" t="n">
+      <c r="M17" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="M17" s="12" t="n">
+      <c r="N17" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1190,42 +1241,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>LOC. ROCCOLINO SS45 BIS</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Emanuele</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="G18" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="H18" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="H18" s="12" t="n">
+      <c r="I18" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="I18" s="12" t="n">
+      <c r="J18" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="J18" s="12" t="n">
+      <c r="K18" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K18" s="12" t="n">
+      <c r="L18" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L18" s="12" t="n">
+      <c r="M18" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="M18" s="12" t="n">
+      <c r="N18" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1244,42 +1300,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>VIALE BORNATA</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Emanuele</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="H19" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="H19" s="12" t="n">
+      <c r="I19" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="I19" s="12" t="n">
+      <c r="J19" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="J19" s="12" t="n">
+      <c r="K19" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K19" s="12" t="n">
+      <c r="L19" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="12" t="n">
+      <c r="M19" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="M19" s="12" t="n">
+      <c r="N19" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1296,26 +1357,28 @@
           <t>BRESCIA</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr"/>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>VIA LAMARMORA  150</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>GRAZIOSI DAVIDE</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="G20" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="H20" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="12" t="n">
+      <c r="I20" s="12" t="n">
         <v>3</v>
-      </c>
-      <c r="I20" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="J20" s="12" t="n">
         <v>0</v>
@@ -1329,7 +1392,10 @@
       <c r="M20" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="N20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>

--- a/docs/files/REPORT_FILTRI/CR - GRAZIOSI DAVIDE.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - GRAZIOSI DAVIDE.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>10</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1449</v>
+        <v>1530</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>972</v>
+        <v>1021</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>751</v>
+        <v>804</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>758</v>
+        <v>801</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>550</v>
+        <v>579</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>482</v>
+        <v>510</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>641</v>
+        <v>678</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,35 +901,35 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>453</v>
+        <v>473</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>543</v>
+        <v>576</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>16</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>3</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>8</v>
@@ -1054,17 +1054,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>11726</t>
+          <t>55973</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>REZZATO</t>
+          <t>BOTTICINO</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>S.S.45 KM.49+300</t>
+          <t>GARIBALDI 18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1113,17 +1113,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>55973</t>
+          <t>11726</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>BOTTICINO</t>
+          <t>REZZATO</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>GARIBALDI 18</t>
+          <t>S.S.45 KM.49+300</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1137,35 +1137,35 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1196,25 +1196,25 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>71</v>
+      </c>
+      <c r="H17" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J17" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="G17" s="12" t="n">
-        <v>69</v>
-      </c>
-      <c r="H17" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I17" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="J17" s="12" t="n">
-        <v>25</v>
-      </c>
       <c r="K17" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>34</v>
@@ -1255,16 +1255,16 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>26</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J18" s="12" t="n">
         <v>13</v>
@@ -1273,10 +1273,10 @@
         <v>1</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>3</v>
@@ -1317,13 +1317,13 @@
         <v>11</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J19" s="12" t="n">
         <v>8</v>
@@ -1372,7 +1372,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/CR - GRAZIOSI DAVIDE.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - GRAZIOSI DAVIDE.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>10</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1530</v>
+        <v>1591</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1021</v>
+        <v>1061</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>804</v>
+        <v>845</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>801</v>
+        <v>832</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>579</v>
+        <v>606</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>83</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>510</v>
+        <v>529</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>678</v>
+        <v>718</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>473</v>
+        <v>493</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>576</v>
+        <v>602</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>7</v>
@@ -960,28 +960,28 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>13</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>4</v>
@@ -1022,13 +1022,13 @@
         <v>46</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>12</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J14" s="12" t="n">
         <v>37</v>
@@ -1078,35 +1078,35 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I15" s="12" t="n">
         <v>1</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
         <v>43</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>17</v>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>4</v>
@@ -1208,7 +1208,7 @@
         <v>10</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>8</v>
@@ -1217,7 +1217,7 @@
         <v>5</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>7</v>
@@ -1255,19 +1255,19 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>26</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>1</v>
@@ -1276,10 +1276,10 @@
         <v>13</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>30</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J19" s="12" t="n">
         <v>8</v>
@@ -1372,7 +1372,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/CR - GRAZIOSI DAVIDE.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - GRAZIOSI DAVIDE.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>10</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1591</v>
+        <v>1673</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1061</v>
+        <v>1120</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>845</v>
+        <v>900</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>832</v>
+        <v>877</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>606</v>
+        <v>652</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>529</v>
+        <v>559</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>718</v>
+        <v>762</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,35 +901,35 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>602</v>
+        <v>637</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>7</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>19</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>4</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>8</v>
@@ -1081,7 +1081,7 @@
         <v>45</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>3</v>
@@ -1099,7 +1099,7 @@
         <v>12</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>17</v>
@@ -1155,7 +1155,7 @@
         <v>10</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>46</v>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
         <v>34</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>4</v>
@@ -1217,10 +1217,10 @@
         <v>5</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>26</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>0</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/CR - GRAZIOSI DAVIDE.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - GRAZIOSI DAVIDE.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>10</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1673</v>
+        <v>1721</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1120</v>
+        <v>1152</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>900</v>
+        <v>929</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>877</v>
+        <v>907</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>652</v>
+        <v>672</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>559</v>
+        <v>577</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>762</v>
+        <v>797</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>637</v>
+        <v>653</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,28 +960,28 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>19</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>4</v>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>17</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>11</v>
@@ -1040,7 +1040,7 @@
         <v>10</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>8</v>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>3</v>
@@ -1090,19 +1090,19 @@
         <v>1</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>44</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>17</v>
@@ -1158,14 +1158,14 @@
         <v>19</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>4</v>
@@ -1208,16 +1208,16 @@
         <v>10</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>5</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>8</v>
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>47</v>
@@ -1264,10 +1264,10 @@
         <v>26</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>1</v>
@@ -1276,7 +1276,7 @@
         <v>14</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>5</v>
@@ -1317,13 +1317,13 @@
         <v>11</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J19" s="12" t="n">
         <v>8</v>
@@ -1372,7 +1372,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/CR - GRAZIOSI DAVIDE.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - GRAZIOSI DAVIDE.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>10</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1721</v>
+        <v>1798</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1152</v>
+        <v>1207</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>929</v>
+        <v>966</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,35 +842,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>907</v>
+        <v>950</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>672</v>
+        <v>689</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>577</v>
+        <v>602</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>797</v>
+        <v>848</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -901,35 +901,35 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>520</v>
+        <v>543</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>653</v>
+        <v>672</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>321</v>
+        <v>350</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>4</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>3</v>
@@ -1090,16 +1090,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>9</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>1</v>
@@ -1158,14 +1158,14 @@
         <v>19</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>4</v>
@@ -1208,7 +1208,7 @@
         <v>10</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>9</v>
@@ -1217,10 +1217,10 @@
         <v>5</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1258,13 +1258,13 @@
         <v>32</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>26</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="J18" s="12" t="n">
         <v>18</v>
@@ -1276,7 +1276,7 @@
         <v>14</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>5</v>
@@ -1317,13 +1317,13 @@
         <v>11</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J19" s="12" t="n">
         <v>8</v>
@@ -1372,7 +1372,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/CR - GRAZIOSI DAVIDE.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - GRAZIOSI DAVIDE.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>10</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1798</v>
+        <v>1872</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1207</v>
+        <v>1262</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>966</v>
+        <v>1010</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>950</v>
+        <v>994</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>689</v>
+        <v>720</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>602</v>
+        <v>632</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>848</v>
+        <v>896</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,35 +901,35 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>672</v>
+        <v>697</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -960,28 +960,28 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>4</v>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>91</v>
+      </c>
+      <c r="H14" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="I14" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="J14" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="G14" s="12" t="n">
-        <v>86</v>
-      </c>
-      <c r="H14" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="I14" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="J14" s="12" t="n">
-        <v>54</v>
-      </c>
       <c r="K14" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,28 +1078,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>13</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>1</v>
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>17</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>10</v>
@@ -1158,7 +1158,7 @@
         <v>19</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>3</v>
@@ -1196,19 +1196,19 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>9</v>
@@ -1217,7 +1217,7 @@
         <v>5</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>9</v>
@@ -1255,19 +1255,19 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>26</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>1</v>
@@ -1276,10 +1276,10 @@
         <v>14</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>30</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J19" s="12" t="n">
         <v>8</v>
@@ -1372,13 +1372,13 @@
         <v>0</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J20" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/CR - GRAZIOSI DAVIDE.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - GRAZIOSI DAVIDE.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>10</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1872</v>
+        <v>1939</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1262</v>
+        <v>1312</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1010</v>
+        <v>1065</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,35 +842,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>994</v>
+        <v>1036</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>720</v>
+        <v>744</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>632</v>
+        <v>664</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>896</v>
+        <v>941</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -901,35 +901,35 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>551</v>
+        <v>566</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>697</v>
+        <v>730</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>361</v>
+        <v>390</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>361</v>
+        <v>384</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>10</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>22</v>
@@ -988,7 +988,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>52</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>3</v>
@@ -1099,7 +1099,7 @@
         <v>13</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>1</v>
@@ -1137,16 +1137,16 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>17</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J16" s="12" t="n">
         <v>26</v>
@@ -1155,13 +1155,13 @@
         <v>10</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>4</v>
@@ -1208,7 +1208,7 @@
         <v>13</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>9</v>
@@ -1217,7 +1217,7 @@
         <v>5</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>9</v>
@@ -1258,13 +1258,13 @@
         <v>33</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="J18" s="12" t="n">
         <v>19</v>
@@ -1276,7 +1276,7 @@
         <v>14</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>6</v>
@@ -1317,13 +1317,13 @@
         <v>11</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="J19" s="12" t="n">
         <v>8</v>
@@ -1372,7 +1372,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/CR - GRAZIOSI DAVIDE.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - GRAZIOSI DAVIDE.xlsx
@@ -684,13 +684,13 @@
         <v>10</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1939</v>
+        <v>1945</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1312</v>
+        <v>0</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1065</v>
+        <v>1051</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>1036</v>
+        <v>1041</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>744</v>
+        <v>734</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>121</v>
@@ -854,7 +854,7 @@
         <v>98</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>664</v>
+        <v>0</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>220</v>
@@ -863,7 +863,7 @@
         <v>377</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>941</v>
+        <v>927</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>118</v>
@@ -904,16 +904,16 @@
         <v>566</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>730</v>
+        <v>718</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>395</v>
+        <v>0</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>152</v>
@@ -922,14 +922,14 @@
         <v>171</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>10</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G13" s="12" t="n">
         <v>73</v>
@@ -972,7 +972,7 @@
         <v>101</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>20</v>
@@ -988,7 +988,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1019,10 +1019,10 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>24</v>
@@ -1031,7 +1031,7 @@
         <v>15</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>17</v>
@@ -1040,14 +1040,14 @@
         <v>11</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>3</v>
@@ -1090,7 +1090,7 @@
         <v>3</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>12</v>
@@ -1099,7 +1099,7 @@
         <v>13</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>1</v>
@@ -1149,7 +1149,7 @@
         <v>7</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>10</v>
@@ -1196,19 +1196,19 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>9</v>
@@ -1261,13 +1261,13 @@
         <v>56</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>1</v>
@@ -1314,19 +1314,19 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>19</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>59</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>1</v>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
